--- a/public/plantillas/plantilla-store-may.xlsx
+++ b/public/plantillas/plantilla-store-may.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Productos" sheetId="1" r:id="Reb58154aaf7c4eeb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Opciones válidas" sheetId="2" r:id="R29296776f6d140da"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Productos" sheetId="1" r:id="R31e99d6d85d34a03"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instrucciones" sheetId="2" r:id="R4baae35f91344462"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -15,9 +15,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:numFmts count="1">
-    <x:numFmt numFmtId="200" formatCode="0.00"/>
+    <x:numFmt numFmtId="200" formatCode="$#,##0.00"/>
   </x:numFmts>
-  <x:fonts count="3">
+  <x:fonts count="5">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -26,15 +26,27 @@
       <x:b/>
       <x:sz val="10"/>
       <x:color rgb="FFFFFFFF"/>
-      <x:name val="Montserrat"/>
+      <x:name val="Carlito"/>
     </x:font>
     <x:font>
       <x:sz val="10"/>
-      <x:color rgb="FF111315"/>
-      <x:name val="Montserrat"/>
+      <x:color rgb="FF202326"/>
+      <x:name val="Carlito"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="15"/>
+      <x:color rgb="FFFFFFFF"/>
+      <x:name val="Carlito"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="11"/>
+      <x:color rgb="FFFFFFFF"/>
+      <x:name val="Carlito"/>
     </x:font>
   </x:fonts>
-  <x:fills count="4">
+  <x:fills count="6">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -43,12 +55,22 @@
     </x:fill>
     <x:fill>
       <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF292D30"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFF5F6F6"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
         <x:fgColor rgb="FF111315"/>
       </x:patternFill>
     </x:fill>
     <x:fill>
       <x:patternFill patternType="solid">
-        <x:fgColor rgb="FFF4F5F5"/>
+        <x:fgColor rgb="FFF1F2F2"/>
       </x:patternFill>
     </x:fill>
   </x:fills>
@@ -85,28 +107,28 @@
       </x:bottom>
     </x:border>
     <x:border>
-      <x:bottom style="thin">
-        <x:color rgb="FFD2D5D7"/>
-      </x:bottom>
+      <x:right style="thin">
+        <x:color rgb="FFD7DADC"/>
+      </x:right>
     </x:border>
     <x:border>
-      <x:top style="thin">
-        <x:color rgb="FFD2D5D7"/>
-      </x:top>
-      <x:bottom style="thin">
-        <x:color rgb="FFD2D5D7"/>
-      </x:bottom>
+      <x:left style="thin">
+        <x:color rgb="FFD7DADC"/>
+      </x:left>
+      <x:right style="thin">
+        <x:color rgb="FFD7DADC"/>
+      </x:right>
     </x:border>
     <x:border>
-      <x:top style="thin">
-        <x:color rgb="FFD2D5D7"/>
-      </x:top>
+      <x:left style="thin">
+        <x:color rgb="FFD7DADC"/>
+      </x:left>
     </x:border>
   </x:borders>
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="21">
+  <x:cellXfs count="22">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -114,43 +136,77 @@
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="1"/>
+      <x:alignment vertical="center"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="1"/>
+      <x:alignment vertical="center"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center" wrapText="1"/>
+      <x:alignment vertical="center"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="200" fontId="2" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="200" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="200" fontId="2" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="200" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
   </x:cellStyles>
+  <x:dxfs count="2">
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FF27633C"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFEAF4ED"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FF8A3030"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFF8EAEA"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+  </x:dxfs>
 </x:styleSheet>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="CatalogoStoreMay" displayName="CatalogoStoreMay" ref="A1:H2" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:H2"/>
+  <x:tableColumns count="8">
+    <x:tableColumn id="1" name="ARTICULO"/>
+    <x:tableColumn id="2" name="MODELO"/>
+    <x:tableColumn id="3" name="MARCA"/>
+    <x:tableColumn id="4" name="COLOR"/>
+    <x:tableColumn id="5" name="TALLA"/>
+    <x:tableColumn id="6" name="V. MARCA"/>
+    <x:tableColumn id="7" name="P.ECUA"/>
+    <x:tableColumn id="8" name="ESTADO"/>
+  </x:tableColumns>
+  <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</x:table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -348,1599 +404,2078 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="28" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="34" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="18" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="24" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="18" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="16" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="15" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
     <x:col min="6" max="6" width="14" hidden="0" customWidth="1"/>
     <x:col min="7" max="7" width="14" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="12" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="22" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="24" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="27" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="14" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" ht="34" customHeight="1">
-      <x:c r="A1" s="9" t="str">
-        <x:v>nombre</x:v>
+    <x:row r="1" ht="25" customHeight="1">
+      <x:c r="A1" s="6" t="str">
+        <x:v>ARTICULO</x:v>
       </x:c>
-      <x:c r="B1" s="10" t="str">
-        <x:v>descripcion</x:v>
+      <x:c r="B1" s="7" t="str">
+        <x:v>MODELO</x:v>
       </x:c>
-      <x:c r="C1" s="10" t="str">
-        <x:v>marca</x:v>
+      <x:c r="C1" s="7" t="str">
+        <x:v>MARCA</x:v>
       </x:c>
-      <x:c r="D1" s="10" t="str">
-        <x:v>categoria</x:v>
+      <x:c r="D1" s="7" t="str">
+        <x:v>COLOR</x:v>
       </x:c>
-      <x:c r="E1" s="10" t="str">
-        <x:v>tipo</x:v>
+      <x:c r="E1" s="7" t="str">
+        <x:v>TALLA</x:v>
       </x:c>
-      <x:c r="F1" s="10" t="str">
-        <x:v>color</x:v>
+      <x:c r="F1" s="7" t="str">
+        <x:v>V. MARCA</x:v>
       </x:c>
-      <x:c r="G1" s="10" t="str">
-        <x:v>genero</x:v>
+      <x:c r="G1" s="7" t="str">
+        <x:v>P.ECUA</x:v>
       </x:c>
-      <x:c r="H1" s="10" t="str">
-        <x:v>precio</x:v>
+      <x:c r="H1" s="8" t="str">
+        <x:v>ESTADO</x:v>
       </x:c>
-      <x:c r="I1" s="10" t="str">
-        <x:v>tallas_disponibles</x:v>
+    </x:row>
+    <x:row r="2" ht="24" customHeight="1">
+      <x:c r="A2" s="11" t="str">
+        <x:v>Bolso</x:v>
       </x:c>
-      <x:c r="J1" s="10" t="str">
-        <x:v>estado</x:v>
+      <x:c r="B2" s="12" t="str">
+        <x:v>Handbag White</x:v>
       </x:c>
-      <x:c r="K1" s="11" t="str">
-        <x:v>nombre_archivo_foto</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="2" ht="44" customHeight="1">
-      <x:c r="A2" s="16" t="str">
-        <x:v>Bolso Adidas Handbag White</x:v>
-      </x:c>
-      <x:c r="B2" s="16" t="str">
-        <x:v>Bolso de lona, correa ajustable</x:v>
-      </x:c>
-      <x:c r="C2" s="16" t="str">
+      <x:c r="C2" s="12" t="str">
         <x:v>Adidas</x:v>
       </x:c>
-      <x:c r="D2" s="16" t="str">
-        <x:v>Mujer</x:v>
-      </x:c>
-      <x:c r="E2" s="16" t="str">
-        <x:v>Bolso</x:v>
-      </x:c>
-      <x:c r="F2" s="16" t="str">
+      <x:c r="D2" s="12" t="str">
         <x:v>Negro</x:v>
       </x:c>
-      <x:c r="G2" s="16" t="str">
-        <x:v>Mujer</x:v>
+      <x:c r="E2" s="12" t="str">
+        <x:v>Consultar</x:v>
       </x:c>
-      <x:c r="H2" s="17" t="n">
+      <x:c r="F2" s="14" t="n">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="G2" s="14" t="n">
         <x:v>45</x:v>
       </x:c>
-      <x:c r="I2" s="16" t="str">
-        <x:v>Consultar / S,M,L</x:v>
+      <x:c r="H2" s="13" t="str">
+        <x:v>STOCK</x:v>
       </x:c>
-      <x:c r="J2" s="16" t="str">
-        <x:v>Disponible</x:v>
-      </x:c>
-      <x:c r="K2" s="16" t="str">
-        <x:v>bolso-adidas-01.jpg</x:v>
-      </x:c>
     </x:row>
     <x:row r="3">
-      <x:c r="H3" s="18"/>
+      <x:c r="F3" s="15"/>
+      <x:c r="G3" s="15"/>
     </x:row>
     <x:row r="4">
-      <x:c r="H4" s="18"/>
+      <x:c r="F4" s="15"/>
+      <x:c r="G4" s="15"/>
     </x:row>
     <x:row r="5">
-      <x:c r="H5" s="18"/>
+      <x:c r="F5" s="15"/>
+      <x:c r="G5" s="15"/>
     </x:row>
     <x:row r="6">
-      <x:c r="H6" s="18"/>
+      <x:c r="F6" s="15"/>
+      <x:c r="G6" s="15"/>
     </x:row>
     <x:row r="7">
-      <x:c r="H7" s="18"/>
+      <x:c r="F7" s="15"/>
+      <x:c r="G7" s="15"/>
     </x:row>
     <x:row r="8">
-      <x:c r="H8" s="18"/>
+      <x:c r="F8" s="15"/>
+      <x:c r="G8" s="15"/>
     </x:row>
     <x:row r="9">
-      <x:c r="H9" s="18"/>
+      <x:c r="F9" s="15"/>
+      <x:c r="G9" s="15"/>
     </x:row>
     <x:row r="10">
-      <x:c r="H10" s="18"/>
+      <x:c r="F10" s="15"/>
+      <x:c r="G10" s="15"/>
     </x:row>
     <x:row r="11">
-      <x:c r="H11" s="18"/>
+      <x:c r="F11" s="15"/>
+      <x:c r="G11" s="15"/>
     </x:row>
     <x:row r="12">
-      <x:c r="H12" s="18"/>
+      <x:c r="F12" s="15"/>
+      <x:c r="G12" s="15"/>
     </x:row>
     <x:row r="13">
-      <x:c r="H13" s="18"/>
+      <x:c r="F13" s="15"/>
+      <x:c r="G13" s="15"/>
     </x:row>
     <x:row r="14">
-      <x:c r="H14" s="18"/>
+      <x:c r="F14" s="15"/>
+      <x:c r="G14" s="15"/>
     </x:row>
     <x:row r="15">
-      <x:c r="H15" s="18"/>
+      <x:c r="F15" s="15"/>
+      <x:c r="G15" s="15"/>
     </x:row>
     <x:row r="16">
-      <x:c r="H16" s="18"/>
+      <x:c r="F16" s="15"/>
+      <x:c r="G16" s="15"/>
     </x:row>
     <x:row r="17">
-      <x:c r="H17" s="18"/>
+      <x:c r="F17" s="15"/>
+      <x:c r="G17" s="15"/>
     </x:row>
     <x:row r="18">
-      <x:c r="H18" s="18"/>
+      <x:c r="F18" s="15"/>
+      <x:c r="G18" s="15"/>
     </x:row>
     <x:row r="19">
-      <x:c r="H19" s="18"/>
+      <x:c r="F19" s="15"/>
+      <x:c r="G19" s="15"/>
     </x:row>
     <x:row r="20">
-      <x:c r="H20" s="18"/>
+      <x:c r="F20" s="15"/>
+      <x:c r="G20" s="15"/>
     </x:row>
     <x:row r="21">
-      <x:c r="H21" s="18"/>
+      <x:c r="F21" s="15"/>
+      <x:c r="G21" s="15"/>
     </x:row>
     <x:row r="22">
-      <x:c r="H22" s="18"/>
+      <x:c r="F22" s="15"/>
+      <x:c r="G22" s="15"/>
     </x:row>
     <x:row r="23">
-      <x:c r="H23" s="18"/>
+      <x:c r="F23" s="15"/>
+      <x:c r="G23" s="15"/>
     </x:row>
     <x:row r="24">
-      <x:c r="H24" s="18"/>
+      <x:c r="F24" s="15"/>
+      <x:c r="G24" s="15"/>
     </x:row>
     <x:row r="25">
-      <x:c r="H25" s="18"/>
+      <x:c r="F25" s="15"/>
+      <x:c r="G25" s="15"/>
     </x:row>
     <x:row r="26">
-      <x:c r="H26" s="18"/>
+      <x:c r="F26" s="15"/>
+      <x:c r="G26" s="15"/>
     </x:row>
     <x:row r="27">
-      <x:c r="H27" s="18"/>
+      <x:c r="F27" s="15"/>
+      <x:c r="G27" s="15"/>
     </x:row>
     <x:row r="28">
-      <x:c r="H28" s="18"/>
+      <x:c r="F28" s="15"/>
+      <x:c r="G28" s="15"/>
     </x:row>
     <x:row r="29">
-      <x:c r="H29" s="18"/>
+      <x:c r="F29" s="15"/>
+      <x:c r="G29" s="15"/>
     </x:row>
     <x:row r="30">
-      <x:c r="H30" s="18"/>
+      <x:c r="F30" s="15"/>
+      <x:c r="G30" s="15"/>
     </x:row>
     <x:row r="31">
-      <x:c r="H31" s="18"/>
+      <x:c r="F31" s="15"/>
+      <x:c r="G31" s="15"/>
     </x:row>
     <x:row r="32">
-      <x:c r="H32" s="18"/>
+      <x:c r="F32" s="15"/>
+      <x:c r="G32" s="15"/>
     </x:row>
     <x:row r="33">
-      <x:c r="H33" s="18"/>
+      <x:c r="F33" s="15"/>
+      <x:c r="G33" s="15"/>
     </x:row>
     <x:row r="34">
-      <x:c r="H34" s="18"/>
+      <x:c r="F34" s="15"/>
+      <x:c r="G34" s="15"/>
     </x:row>
     <x:row r="35">
-      <x:c r="H35" s="18"/>
+      <x:c r="F35" s="15"/>
+      <x:c r="G35" s="15"/>
     </x:row>
     <x:row r="36">
-      <x:c r="H36" s="18"/>
+      <x:c r="F36" s="15"/>
+      <x:c r="G36" s="15"/>
     </x:row>
     <x:row r="37">
-      <x:c r="H37" s="18"/>
+      <x:c r="F37" s="15"/>
+      <x:c r="G37" s="15"/>
     </x:row>
     <x:row r="38">
-      <x:c r="H38" s="18"/>
+      <x:c r="F38" s="15"/>
+      <x:c r="G38" s="15"/>
     </x:row>
     <x:row r="39">
-      <x:c r="H39" s="18"/>
+      <x:c r="F39" s="15"/>
+      <x:c r="G39" s="15"/>
     </x:row>
     <x:row r="40">
-      <x:c r="H40" s="18"/>
+      <x:c r="F40" s="15"/>
+      <x:c r="G40" s="15"/>
     </x:row>
     <x:row r="41">
-      <x:c r="H41" s="18"/>
+      <x:c r="F41" s="15"/>
+      <x:c r="G41" s="15"/>
     </x:row>
     <x:row r="42">
-      <x:c r="H42" s="18"/>
+      <x:c r="F42" s="15"/>
+      <x:c r="G42" s="15"/>
     </x:row>
     <x:row r="43">
-      <x:c r="H43" s="18"/>
+      <x:c r="F43" s="15"/>
+      <x:c r="G43" s="15"/>
     </x:row>
     <x:row r="44">
-      <x:c r="H44" s="18"/>
+      <x:c r="F44" s="15"/>
+      <x:c r="G44" s="15"/>
     </x:row>
     <x:row r="45">
-      <x:c r="H45" s="18"/>
+      <x:c r="F45" s="15"/>
+      <x:c r="G45" s="15"/>
     </x:row>
     <x:row r="46">
-      <x:c r="H46" s="18"/>
+      <x:c r="F46" s="15"/>
+      <x:c r="G46" s="15"/>
     </x:row>
     <x:row r="47">
-      <x:c r="H47" s="18"/>
+      <x:c r="F47" s="15"/>
+      <x:c r="G47" s="15"/>
     </x:row>
     <x:row r="48">
-      <x:c r="H48" s="18"/>
+      <x:c r="F48" s="15"/>
+      <x:c r="G48" s="15"/>
     </x:row>
     <x:row r="49">
-      <x:c r="H49" s="18"/>
+      <x:c r="F49" s="15"/>
+      <x:c r="G49" s="15"/>
     </x:row>
     <x:row r="50">
-      <x:c r="H50" s="18"/>
+      <x:c r="F50" s="15"/>
+      <x:c r="G50" s="15"/>
     </x:row>
     <x:row r="51">
-      <x:c r="H51" s="18"/>
+      <x:c r="F51" s="15"/>
+      <x:c r="G51" s="15"/>
     </x:row>
     <x:row r="52">
-      <x:c r="H52" s="18"/>
+      <x:c r="F52" s="15"/>
+      <x:c r="G52" s="15"/>
     </x:row>
     <x:row r="53">
-      <x:c r="H53" s="18"/>
+      <x:c r="F53" s="15"/>
+      <x:c r="G53" s="15"/>
     </x:row>
     <x:row r="54">
-      <x:c r="H54" s="18"/>
+      <x:c r="F54" s="15"/>
+      <x:c r="G54" s="15"/>
     </x:row>
     <x:row r="55">
-      <x:c r="H55" s="18"/>
+      <x:c r="F55" s="15"/>
+      <x:c r="G55" s="15"/>
     </x:row>
     <x:row r="56">
-      <x:c r="H56" s="18"/>
+      <x:c r="F56" s="15"/>
+      <x:c r="G56" s="15"/>
     </x:row>
     <x:row r="57">
-      <x:c r="H57" s="18"/>
+      <x:c r="F57" s="15"/>
+      <x:c r="G57" s="15"/>
     </x:row>
     <x:row r="58">
-      <x:c r="H58" s="18"/>
+      <x:c r="F58" s="15"/>
+      <x:c r="G58" s="15"/>
     </x:row>
     <x:row r="59">
-      <x:c r="H59" s="18"/>
+      <x:c r="F59" s="15"/>
+      <x:c r="G59" s="15"/>
     </x:row>
     <x:row r="60">
-      <x:c r="H60" s="18"/>
+      <x:c r="F60" s="15"/>
+      <x:c r="G60" s="15"/>
     </x:row>
     <x:row r="61">
-      <x:c r="H61" s="18"/>
+      <x:c r="F61" s="15"/>
+      <x:c r="G61" s="15"/>
     </x:row>
     <x:row r="62">
-      <x:c r="H62" s="18"/>
+      <x:c r="F62" s="15"/>
+      <x:c r="G62" s="15"/>
     </x:row>
     <x:row r="63">
-      <x:c r="H63" s="18"/>
+      <x:c r="F63" s="15"/>
+      <x:c r="G63" s="15"/>
     </x:row>
     <x:row r="64">
-      <x:c r="H64" s="18"/>
+      <x:c r="F64" s="15"/>
+      <x:c r="G64" s="15"/>
     </x:row>
     <x:row r="65">
-      <x:c r="H65" s="18"/>
+      <x:c r="F65" s="15"/>
+      <x:c r="G65" s="15"/>
     </x:row>
     <x:row r="66">
-      <x:c r="H66" s="18"/>
+      <x:c r="F66" s="15"/>
+      <x:c r="G66" s="15"/>
     </x:row>
     <x:row r="67">
-      <x:c r="H67" s="18"/>
+      <x:c r="F67" s="15"/>
+      <x:c r="G67" s="15"/>
     </x:row>
     <x:row r="68">
-      <x:c r="H68" s="18"/>
+      <x:c r="F68" s="15"/>
+      <x:c r="G68" s="15"/>
     </x:row>
     <x:row r="69">
-      <x:c r="H69" s="18"/>
+      <x:c r="F69" s="15"/>
+      <x:c r="G69" s="15"/>
     </x:row>
     <x:row r="70">
-      <x:c r="H70" s="18"/>
+      <x:c r="F70" s="15"/>
+      <x:c r="G70" s="15"/>
     </x:row>
     <x:row r="71">
-      <x:c r="H71" s="18"/>
+      <x:c r="F71" s="15"/>
+      <x:c r="G71" s="15"/>
     </x:row>
     <x:row r="72">
-      <x:c r="H72" s="18"/>
+      <x:c r="F72" s="15"/>
+      <x:c r="G72" s="15"/>
     </x:row>
     <x:row r="73">
-      <x:c r="H73" s="18"/>
+      <x:c r="F73" s="15"/>
+      <x:c r="G73" s="15"/>
     </x:row>
     <x:row r="74">
-      <x:c r="H74" s="18"/>
+      <x:c r="F74" s="15"/>
+      <x:c r="G74" s="15"/>
     </x:row>
     <x:row r="75">
-      <x:c r="H75" s="18"/>
+      <x:c r="F75" s="15"/>
+      <x:c r="G75" s="15"/>
     </x:row>
     <x:row r="76">
-      <x:c r="H76" s="18"/>
+      <x:c r="F76" s="15"/>
+      <x:c r="G76" s="15"/>
     </x:row>
     <x:row r="77">
-      <x:c r="H77" s="18"/>
+      <x:c r="F77" s="15"/>
+      <x:c r="G77" s="15"/>
     </x:row>
     <x:row r="78">
-      <x:c r="H78" s="18"/>
+      <x:c r="F78" s="15"/>
+      <x:c r="G78" s="15"/>
     </x:row>
     <x:row r="79">
-      <x:c r="H79" s="18"/>
+      <x:c r="F79" s="15"/>
+      <x:c r="G79" s="15"/>
     </x:row>
     <x:row r="80">
-      <x:c r="H80" s="18"/>
+      <x:c r="F80" s="15"/>
+      <x:c r="G80" s="15"/>
     </x:row>
     <x:row r="81">
-      <x:c r="H81" s="18"/>
+      <x:c r="F81" s="15"/>
+      <x:c r="G81" s="15"/>
     </x:row>
     <x:row r="82">
-      <x:c r="H82" s="18"/>
+      <x:c r="F82" s="15"/>
+      <x:c r="G82" s="15"/>
     </x:row>
     <x:row r="83">
-      <x:c r="H83" s="18"/>
+      <x:c r="F83" s="15"/>
+      <x:c r="G83" s="15"/>
     </x:row>
     <x:row r="84">
-      <x:c r="H84" s="18"/>
+      <x:c r="F84" s="15"/>
+      <x:c r="G84" s="15"/>
     </x:row>
     <x:row r="85">
-      <x:c r="H85" s="18"/>
+      <x:c r="F85" s="15"/>
+      <x:c r="G85" s="15"/>
     </x:row>
     <x:row r="86">
-      <x:c r="H86" s="18"/>
+      <x:c r="F86" s="15"/>
+      <x:c r="G86" s="15"/>
     </x:row>
     <x:row r="87">
-      <x:c r="H87" s="18"/>
+      <x:c r="F87" s="15"/>
+      <x:c r="G87" s="15"/>
     </x:row>
     <x:row r="88">
-      <x:c r="H88" s="18"/>
+      <x:c r="F88" s="15"/>
+      <x:c r="G88" s="15"/>
     </x:row>
     <x:row r="89">
-      <x:c r="H89" s="18"/>
+      <x:c r="F89" s="15"/>
+      <x:c r="G89" s="15"/>
     </x:row>
     <x:row r="90">
-      <x:c r="H90" s="18"/>
+      <x:c r="F90" s="15"/>
+      <x:c r="G90" s="15"/>
     </x:row>
     <x:row r="91">
-      <x:c r="H91" s="18"/>
+      <x:c r="F91" s="15"/>
+      <x:c r="G91" s="15"/>
     </x:row>
     <x:row r="92">
-      <x:c r="H92" s="18"/>
+      <x:c r="F92" s="15"/>
+      <x:c r="G92" s="15"/>
     </x:row>
     <x:row r="93">
-      <x:c r="H93" s="18"/>
+      <x:c r="F93" s="15"/>
+      <x:c r="G93" s="15"/>
     </x:row>
     <x:row r="94">
-      <x:c r="H94" s="18"/>
+      <x:c r="F94" s="15"/>
+      <x:c r="G94" s="15"/>
     </x:row>
     <x:row r="95">
-      <x:c r="H95" s="18"/>
+      <x:c r="F95" s="15"/>
+      <x:c r="G95" s="15"/>
     </x:row>
     <x:row r="96">
-      <x:c r="H96" s="18"/>
+      <x:c r="F96" s="15"/>
+      <x:c r="G96" s="15"/>
     </x:row>
     <x:row r="97">
-      <x:c r="H97" s="18"/>
+      <x:c r="F97" s="15"/>
+      <x:c r="G97" s="15"/>
     </x:row>
     <x:row r="98">
-      <x:c r="H98" s="18"/>
+      <x:c r="F98" s="15"/>
+      <x:c r="G98" s="15"/>
     </x:row>
     <x:row r="99">
-      <x:c r="H99" s="18"/>
+      <x:c r="F99" s="15"/>
+      <x:c r="G99" s="15"/>
     </x:row>
     <x:row r="100">
-      <x:c r="H100" s="18"/>
+      <x:c r="F100" s="15"/>
+      <x:c r="G100" s="15"/>
     </x:row>
     <x:row r="101">
-      <x:c r="H101" s="18"/>
+      <x:c r="F101" s="15"/>
+      <x:c r="G101" s="15"/>
     </x:row>
     <x:row r="102">
-      <x:c r="H102" s="18"/>
+      <x:c r="F102" s="15"/>
+      <x:c r="G102" s="15"/>
     </x:row>
     <x:row r="103">
-      <x:c r="H103" s="18"/>
+      <x:c r="F103" s="15"/>
+      <x:c r="G103" s="15"/>
     </x:row>
     <x:row r="104">
-      <x:c r="H104" s="18"/>
+      <x:c r="F104" s="15"/>
+      <x:c r="G104" s="15"/>
     </x:row>
     <x:row r="105">
-      <x:c r="H105" s="18"/>
+      <x:c r="F105" s="15"/>
+      <x:c r="G105" s="15"/>
     </x:row>
     <x:row r="106">
-      <x:c r="H106" s="18"/>
+      <x:c r="F106" s="15"/>
+      <x:c r="G106" s="15"/>
     </x:row>
     <x:row r="107">
-      <x:c r="H107" s="18"/>
+      <x:c r="F107" s="15"/>
+      <x:c r="G107" s="15"/>
     </x:row>
     <x:row r="108">
-      <x:c r="H108" s="18"/>
+      <x:c r="F108" s="15"/>
+      <x:c r="G108" s="15"/>
     </x:row>
     <x:row r="109">
-      <x:c r="H109" s="18"/>
+      <x:c r="F109" s="15"/>
+      <x:c r="G109" s="15"/>
     </x:row>
     <x:row r="110">
-      <x:c r="H110" s="18"/>
+      <x:c r="F110" s="15"/>
+      <x:c r="G110" s="15"/>
     </x:row>
     <x:row r="111">
-      <x:c r="H111" s="18"/>
+      <x:c r="F111" s="15"/>
+      <x:c r="G111" s="15"/>
     </x:row>
     <x:row r="112">
-      <x:c r="H112" s="18"/>
+      <x:c r="F112" s="15"/>
+      <x:c r="G112" s="15"/>
     </x:row>
     <x:row r="113">
-      <x:c r="H113" s="18"/>
+      <x:c r="F113" s="15"/>
+      <x:c r="G113" s="15"/>
     </x:row>
     <x:row r="114">
-      <x:c r="H114" s="18"/>
+      <x:c r="F114" s="15"/>
+      <x:c r="G114" s="15"/>
     </x:row>
     <x:row r="115">
-      <x:c r="H115" s="18"/>
+      <x:c r="F115" s="15"/>
+      <x:c r="G115" s="15"/>
     </x:row>
     <x:row r="116">
-      <x:c r="H116" s="18"/>
+      <x:c r="F116" s="15"/>
+      <x:c r="G116" s="15"/>
     </x:row>
     <x:row r="117">
-      <x:c r="H117" s="18"/>
+      <x:c r="F117" s="15"/>
+      <x:c r="G117" s="15"/>
     </x:row>
     <x:row r="118">
-      <x:c r="H118" s="18"/>
+      <x:c r="F118" s="15"/>
+      <x:c r="G118" s="15"/>
     </x:row>
     <x:row r="119">
-      <x:c r="H119" s="18"/>
+      <x:c r="F119" s="15"/>
+      <x:c r="G119" s="15"/>
     </x:row>
     <x:row r="120">
-      <x:c r="H120" s="18"/>
+      <x:c r="F120" s="15"/>
+      <x:c r="G120" s="15"/>
     </x:row>
     <x:row r="121">
-      <x:c r="H121" s="18"/>
+      <x:c r="F121" s="15"/>
+      <x:c r="G121" s="15"/>
     </x:row>
     <x:row r="122">
-      <x:c r="H122" s="18"/>
+      <x:c r="F122" s="15"/>
+      <x:c r="G122" s="15"/>
     </x:row>
     <x:row r="123">
-      <x:c r="H123" s="18"/>
+      <x:c r="F123" s="15"/>
+      <x:c r="G123" s="15"/>
     </x:row>
     <x:row r="124">
-      <x:c r="H124" s="18"/>
+      <x:c r="F124" s="15"/>
+      <x:c r="G124" s="15"/>
     </x:row>
     <x:row r="125">
-      <x:c r="H125" s="18"/>
+      <x:c r="F125" s="15"/>
+      <x:c r="G125" s="15"/>
     </x:row>
     <x:row r="126">
-      <x:c r="H126" s="18"/>
+      <x:c r="F126" s="15"/>
+      <x:c r="G126" s="15"/>
     </x:row>
     <x:row r="127">
-      <x:c r="H127" s="18"/>
+      <x:c r="F127" s="15"/>
+      <x:c r="G127" s="15"/>
     </x:row>
     <x:row r="128">
-      <x:c r="H128" s="18"/>
+      <x:c r="F128" s="15"/>
+      <x:c r="G128" s="15"/>
     </x:row>
     <x:row r="129">
-      <x:c r="H129" s="18"/>
+      <x:c r="F129" s="15"/>
+      <x:c r="G129" s="15"/>
     </x:row>
     <x:row r="130">
-      <x:c r="H130" s="18"/>
+      <x:c r="F130" s="15"/>
+      <x:c r="G130" s="15"/>
     </x:row>
     <x:row r="131">
-      <x:c r="H131" s="18"/>
+      <x:c r="F131" s="15"/>
+      <x:c r="G131" s="15"/>
     </x:row>
     <x:row r="132">
-      <x:c r="H132" s="18"/>
+      <x:c r="F132" s="15"/>
+      <x:c r="G132" s="15"/>
     </x:row>
     <x:row r="133">
-      <x:c r="H133" s="18"/>
+      <x:c r="F133" s="15"/>
+      <x:c r="G133" s="15"/>
     </x:row>
     <x:row r="134">
-      <x:c r="H134" s="18"/>
+      <x:c r="F134" s="15"/>
+      <x:c r="G134" s="15"/>
     </x:row>
     <x:row r="135">
-      <x:c r="H135" s="18"/>
+      <x:c r="F135" s="15"/>
+      <x:c r="G135" s="15"/>
     </x:row>
     <x:row r="136">
-      <x:c r="H136" s="18"/>
+      <x:c r="F136" s="15"/>
+      <x:c r="G136" s="15"/>
     </x:row>
     <x:row r="137">
-      <x:c r="H137" s="18"/>
+      <x:c r="F137" s="15"/>
+      <x:c r="G137" s="15"/>
     </x:row>
     <x:row r="138">
-      <x:c r="H138" s="18"/>
+      <x:c r="F138" s="15"/>
+      <x:c r="G138" s="15"/>
     </x:row>
     <x:row r="139">
-      <x:c r="H139" s="18"/>
+      <x:c r="F139" s="15"/>
+      <x:c r="G139" s="15"/>
     </x:row>
     <x:row r="140">
-      <x:c r="H140" s="18"/>
+      <x:c r="F140" s="15"/>
+      <x:c r="G140" s="15"/>
     </x:row>
     <x:row r="141">
-      <x:c r="H141" s="18"/>
+      <x:c r="F141" s="15"/>
+      <x:c r="G141" s="15"/>
     </x:row>
     <x:row r="142">
-      <x:c r="H142" s="18"/>
+      <x:c r="F142" s="15"/>
+      <x:c r="G142" s="15"/>
     </x:row>
     <x:row r="143">
-      <x:c r="H143" s="18"/>
+      <x:c r="F143" s="15"/>
+      <x:c r="G143" s="15"/>
     </x:row>
     <x:row r="144">
-      <x:c r="H144" s="18"/>
+      <x:c r="F144" s="15"/>
+      <x:c r="G144" s="15"/>
     </x:row>
     <x:row r="145">
-      <x:c r="H145" s="18"/>
+      <x:c r="F145" s="15"/>
+      <x:c r="G145" s="15"/>
     </x:row>
     <x:row r="146">
-      <x:c r="H146" s="18"/>
+      <x:c r="F146" s="15"/>
+      <x:c r="G146" s="15"/>
     </x:row>
     <x:row r="147">
-      <x:c r="H147" s="18"/>
+      <x:c r="F147" s="15"/>
+      <x:c r="G147" s="15"/>
     </x:row>
     <x:row r="148">
-      <x:c r="H148" s="18"/>
+      <x:c r="F148" s="15"/>
+      <x:c r="G148" s="15"/>
     </x:row>
     <x:row r="149">
-      <x:c r="H149" s="18"/>
+      <x:c r="F149" s="15"/>
+      <x:c r="G149" s="15"/>
     </x:row>
     <x:row r="150">
-      <x:c r="H150" s="18"/>
+      <x:c r="F150" s="15"/>
+      <x:c r="G150" s="15"/>
     </x:row>
     <x:row r="151">
-      <x:c r="H151" s="18"/>
+      <x:c r="F151" s="15"/>
+      <x:c r="G151" s="15"/>
     </x:row>
     <x:row r="152">
-      <x:c r="H152" s="18"/>
+      <x:c r="F152" s="15"/>
+      <x:c r="G152" s="15"/>
     </x:row>
     <x:row r="153">
-      <x:c r="H153" s="18"/>
+      <x:c r="F153" s="15"/>
+      <x:c r="G153" s="15"/>
     </x:row>
     <x:row r="154">
-      <x:c r="H154" s="18"/>
+      <x:c r="F154" s="15"/>
+      <x:c r="G154" s="15"/>
     </x:row>
     <x:row r="155">
-      <x:c r="H155" s="18"/>
+      <x:c r="F155" s="15"/>
+      <x:c r="G155" s="15"/>
     </x:row>
     <x:row r="156">
-      <x:c r="H156" s="18"/>
+      <x:c r="F156" s="15"/>
+      <x:c r="G156" s="15"/>
     </x:row>
     <x:row r="157">
-      <x:c r="H157" s="18"/>
+      <x:c r="F157" s="15"/>
+      <x:c r="G157" s="15"/>
     </x:row>
     <x:row r="158">
-      <x:c r="H158" s="18"/>
+      <x:c r="F158" s="15"/>
+      <x:c r="G158" s="15"/>
     </x:row>
     <x:row r="159">
-      <x:c r="H159" s="18"/>
+      <x:c r="F159" s="15"/>
+      <x:c r="G159" s="15"/>
     </x:row>
     <x:row r="160">
-      <x:c r="H160" s="18"/>
+      <x:c r="F160" s="15"/>
+      <x:c r="G160" s="15"/>
     </x:row>
     <x:row r="161">
-      <x:c r="H161" s="18"/>
+      <x:c r="F161" s="15"/>
+      <x:c r="G161" s="15"/>
     </x:row>
     <x:row r="162">
-      <x:c r="H162" s="18"/>
+      <x:c r="F162" s="15"/>
+      <x:c r="G162" s="15"/>
     </x:row>
     <x:row r="163">
-      <x:c r="H163" s="18"/>
+      <x:c r="F163" s="15"/>
+      <x:c r="G163" s="15"/>
     </x:row>
     <x:row r="164">
-      <x:c r="H164" s="18"/>
+      <x:c r="F164" s="15"/>
+      <x:c r="G164" s="15"/>
     </x:row>
     <x:row r="165">
-      <x:c r="H165" s="18"/>
+      <x:c r="F165" s="15"/>
+      <x:c r="G165" s="15"/>
     </x:row>
     <x:row r="166">
-      <x:c r="H166" s="18"/>
+      <x:c r="F166" s="15"/>
+      <x:c r="G166" s="15"/>
     </x:row>
     <x:row r="167">
-      <x:c r="H167" s="18"/>
+      <x:c r="F167" s="15"/>
+      <x:c r="G167" s="15"/>
     </x:row>
     <x:row r="168">
-      <x:c r="H168" s="18"/>
+      <x:c r="F168" s="15"/>
+      <x:c r="G168" s="15"/>
     </x:row>
     <x:row r="169">
-      <x:c r="H169" s="18"/>
+      <x:c r="F169" s="15"/>
+      <x:c r="G169" s="15"/>
     </x:row>
     <x:row r="170">
-      <x:c r="H170" s="18"/>
+      <x:c r="F170" s="15"/>
+      <x:c r="G170" s="15"/>
     </x:row>
     <x:row r="171">
-      <x:c r="H171" s="18"/>
+      <x:c r="F171" s="15"/>
+      <x:c r="G171" s="15"/>
     </x:row>
     <x:row r="172">
-      <x:c r="H172" s="18"/>
+      <x:c r="F172" s="15"/>
+      <x:c r="G172" s="15"/>
     </x:row>
     <x:row r="173">
-      <x:c r="H173" s="18"/>
+      <x:c r="F173" s="15"/>
+      <x:c r="G173" s="15"/>
     </x:row>
     <x:row r="174">
-      <x:c r="H174" s="18"/>
+      <x:c r="F174" s="15"/>
+      <x:c r="G174" s="15"/>
     </x:row>
     <x:row r="175">
-      <x:c r="H175" s="18"/>
+      <x:c r="F175" s="15"/>
+      <x:c r="G175" s="15"/>
     </x:row>
     <x:row r="176">
-      <x:c r="H176" s="18"/>
+      <x:c r="F176" s="15"/>
+      <x:c r="G176" s="15"/>
     </x:row>
     <x:row r="177">
-      <x:c r="H177" s="18"/>
+      <x:c r="F177" s="15"/>
+      <x:c r="G177" s="15"/>
     </x:row>
     <x:row r="178">
-      <x:c r="H178" s="18"/>
+      <x:c r="F178" s="15"/>
+      <x:c r="G178" s="15"/>
     </x:row>
     <x:row r="179">
-      <x:c r="H179" s="18"/>
+      <x:c r="F179" s="15"/>
+      <x:c r="G179" s="15"/>
     </x:row>
     <x:row r="180">
-      <x:c r="H180" s="18"/>
+      <x:c r="F180" s="15"/>
+      <x:c r="G180" s="15"/>
     </x:row>
     <x:row r="181">
-      <x:c r="H181" s="18"/>
+      <x:c r="F181" s="15"/>
+      <x:c r="G181" s="15"/>
     </x:row>
     <x:row r="182">
-      <x:c r="H182" s="18"/>
+      <x:c r="F182" s="15"/>
+      <x:c r="G182" s="15"/>
     </x:row>
     <x:row r="183">
-      <x:c r="H183" s="18"/>
+      <x:c r="F183" s="15"/>
+      <x:c r="G183" s="15"/>
     </x:row>
     <x:row r="184">
-      <x:c r="H184" s="18"/>
+      <x:c r="F184" s="15"/>
+      <x:c r="G184" s="15"/>
     </x:row>
     <x:row r="185">
-      <x:c r="H185" s="18"/>
+      <x:c r="F185" s="15"/>
+      <x:c r="G185" s="15"/>
     </x:row>
     <x:row r="186">
-      <x:c r="H186" s="18"/>
+      <x:c r="F186" s="15"/>
+      <x:c r="G186" s="15"/>
     </x:row>
     <x:row r="187">
-      <x:c r="H187" s="18"/>
+      <x:c r="F187" s="15"/>
+      <x:c r="G187" s="15"/>
     </x:row>
     <x:row r="188">
-      <x:c r="H188" s="18"/>
+      <x:c r="F188" s="15"/>
+      <x:c r="G188" s="15"/>
     </x:row>
     <x:row r="189">
-      <x:c r="H189" s="18"/>
+      <x:c r="F189" s="15"/>
+      <x:c r="G189" s="15"/>
     </x:row>
     <x:row r="190">
-      <x:c r="H190" s="18"/>
+      <x:c r="F190" s="15"/>
+      <x:c r="G190" s="15"/>
     </x:row>
     <x:row r="191">
-      <x:c r="H191" s="18"/>
+      <x:c r="F191" s="15"/>
+      <x:c r="G191" s="15"/>
     </x:row>
     <x:row r="192">
-      <x:c r="H192" s="18"/>
+      <x:c r="F192" s="15"/>
+      <x:c r="G192" s="15"/>
     </x:row>
     <x:row r="193">
-      <x:c r="H193" s="18"/>
+      <x:c r="F193" s="15"/>
+      <x:c r="G193" s="15"/>
     </x:row>
     <x:row r="194">
-      <x:c r="H194" s="18"/>
+      <x:c r="F194" s="15"/>
+      <x:c r="G194" s="15"/>
     </x:row>
     <x:row r="195">
-      <x:c r="H195" s="18"/>
+      <x:c r="F195" s="15"/>
+      <x:c r="G195" s="15"/>
     </x:row>
     <x:row r="196">
-      <x:c r="H196" s="18"/>
+      <x:c r="F196" s="15"/>
+      <x:c r="G196" s="15"/>
     </x:row>
     <x:row r="197">
-      <x:c r="H197" s="18"/>
+      <x:c r="F197" s="15"/>
+      <x:c r="G197" s="15"/>
     </x:row>
     <x:row r="198">
-      <x:c r="H198" s="18"/>
+      <x:c r="F198" s="15"/>
+      <x:c r="G198" s="15"/>
     </x:row>
     <x:row r="199">
-      <x:c r="H199" s="18"/>
+      <x:c r="F199" s="15"/>
+      <x:c r="G199" s="15"/>
     </x:row>
     <x:row r="200">
-      <x:c r="H200" s="18"/>
+      <x:c r="F200" s="15"/>
+      <x:c r="G200" s="15"/>
     </x:row>
     <x:row r="201">
-      <x:c r="H201" s="18"/>
+      <x:c r="F201" s="15"/>
+      <x:c r="G201" s="15"/>
     </x:row>
     <x:row r="202">
-      <x:c r="H202" s="18"/>
+      <x:c r="F202" s="15"/>
+      <x:c r="G202" s="15"/>
     </x:row>
     <x:row r="203">
-      <x:c r="H203" s="18"/>
+      <x:c r="F203" s="15"/>
+      <x:c r="G203" s="15"/>
     </x:row>
     <x:row r="204">
-      <x:c r="H204" s="18"/>
+      <x:c r="F204" s="15"/>
+      <x:c r="G204" s="15"/>
     </x:row>
     <x:row r="205">
-      <x:c r="H205" s="18"/>
+      <x:c r="F205" s="15"/>
+      <x:c r="G205" s="15"/>
     </x:row>
     <x:row r="206">
-      <x:c r="H206" s="18"/>
+      <x:c r="F206" s="15"/>
+      <x:c r="G206" s="15"/>
     </x:row>
     <x:row r="207">
-      <x:c r="H207" s="18"/>
+      <x:c r="F207" s="15"/>
+      <x:c r="G207" s="15"/>
     </x:row>
     <x:row r="208">
-      <x:c r="H208" s="18"/>
+      <x:c r="F208" s="15"/>
+      <x:c r="G208" s="15"/>
     </x:row>
     <x:row r="209">
-      <x:c r="H209" s="18"/>
+      <x:c r="F209" s="15"/>
+      <x:c r="G209" s="15"/>
     </x:row>
     <x:row r="210">
-      <x:c r="H210" s="18"/>
+      <x:c r="F210" s="15"/>
+      <x:c r="G210" s="15"/>
     </x:row>
     <x:row r="211">
-      <x:c r="H211" s="18"/>
+      <x:c r="F211" s="15"/>
+      <x:c r="G211" s="15"/>
     </x:row>
     <x:row r="212">
-      <x:c r="H212" s="18"/>
+      <x:c r="F212" s="15"/>
+      <x:c r="G212" s="15"/>
     </x:row>
     <x:row r="213">
-      <x:c r="H213" s="18"/>
+      <x:c r="F213" s="15"/>
+      <x:c r="G213" s="15"/>
     </x:row>
     <x:row r="214">
-      <x:c r="H214" s="18"/>
+      <x:c r="F214" s="15"/>
+      <x:c r="G214" s="15"/>
     </x:row>
     <x:row r="215">
-      <x:c r="H215" s="18"/>
+      <x:c r="F215" s="15"/>
+      <x:c r="G215" s="15"/>
     </x:row>
     <x:row r="216">
-      <x:c r="H216" s="18"/>
+      <x:c r="F216" s="15"/>
+      <x:c r="G216" s="15"/>
     </x:row>
     <x:row r="217">
-      <x:c r="H217" s="18"/>
+      <x:c r="F217" s="15"/>
+      <x:c r="G217" s="15"/>
     </x:row>
     <x:row r="218">
-      <x:c r="H218" s="18"/>
+      <x:c r="F218" s="15"/>
+      <x:c r="G218" s="15"/>
     </x:row>
     <x:row r="219">
-      <x:c r="H219" s="18"/>
+      <x:c r="F219" s="15"/>
+      <x:c r="G219" s="15"/>
     </x:row>
     <x:row r="220">
-      <x:c r="H220" s="18"/>
+      <x:c r="F220" s="15"/>
+      <x:c r="G220" s="15"/>
     </x:row>
     <x:row r="221">
-      <x:c r="H221" s="18"/>
+      <x:c r="F221" s="15"/>
+      <x:c r="G221" s="15"/>
     </x:row>
     <x:row r="222">
-      <x:c r="H222" s="18"/>
+      <x:c r="F222" s="15"/>
+      <x:c r="G222" s="15"/>
     </x:row>
     <x:row r="223">
-      <x:c r="H223" s="18"/>
+      <x:c r="F223" s="15"/>
+      <x:c r="G223" s="15"/>
     </x:row>
     <x:row r="224">
-      <x:c r="H224" s="18"/>
+      <x:c r="F224" s="15"/>
+      <x:c r="G224" s="15"/>
     </x:row>
     <x:row r="225">
-      <x:c r="H225" s="18"/>
+      <x:c r="F225" s="15"/>
+      <x:c r="G225" s="15"/>
     </x:row>
     <x:row r="226">
-      <x:c r="H226" s="18"/>
+      <x:c r="F226" s="15"/>
+      <x:c r="G226" s="15"/>
     </x:row>
     <x:row r="227">
-      <x:c r="H227" s="18"/>
+      <x:c r="F227" s="15"/>
+      <x:c r="G227" s="15"/>
     </x:row>
     <x:row r="228">
-      <x:c r="H228" s="18"/>
+      <x:c r="F228" s="15"/>
+      <x:c r="G228" s="15"/>
     </x:row>
     <x:row r="229">
-      <x:c r="H229" s="18"/>
+      <x:c r="F229" s="15"/>
+      <x:c r="G229" s="15"/>
     </x:row>
     <x:row r="230">
-      <x:c r="H230" s="18"/>
+      <x:c r="F230" s="15"/>
+      <x:c r="G230" s="15"/>
     </x:row>
     <x:row r="231">
-      <x:c r="H231" s="18"/>
+      <x:c r="F231" s="15"/>
+      <x:c r="G231" s="15"/>
     </x:row>
     <x:row r="232">
-      <x:c r="H232" s="18"/>
+      <x:c r="F232" s="15"/>
+      <x:c r="G232" s="15"/>
     </x:row>
     <x:row r="233">
-      <x:c r="H233" s="18"/>
+      <x:c r="F233" s="15"/>
+      <x:c r="G233" s="15"/>
     </x:row>
     <x:row r="234">
-      <x:c r="H234" s="18"/>
+      <x:c r="F234" s="15"/>
+      <x:c r="G234" s="15"/>
     </x:row>
     <x:row r="235">
-      <x:c r="H235" s="18"/>
+      <x:c r="F235" s="15"/>
+      <x:c r="G235" s="15"/>
     </x:row>
     <x:row r="236">
-      <x:c r="H236" s="18"/>
+      <x:c r="F236" s="15"/>
+      <x:c r="G236" s="15"/>
     </x:row>
     <x:row r="237">
-      <x:c r="H237" s="18"/>
+      <x:c r="F237" s="15"/>
+      <x:c r="G237" s="15"/>
     </x:row>
     <x:row r="238">
-      <x:c r="H238" s="18"/>
+      <x:c r="F238" s="15"/>
+      <x:c r="G238" s="15"/>
     </x:row>
     <x:row r="239">
-      <x:c r="H239" s="18"/>
+      <x:c r="F239" s="15"/>
+      <x:c r="G239" s="15"/>
     </x:row>
     <x:row r="240">
-      <x:c r="H240" s="18"/>
+      <x:c r="F240" s="15"/>
+      <x:c r="G240" s="15"/>
     </x:row>
     <x:row r="241">
-      <x:c r="H241" s="18"/>
+      <x:c r="F241" s="15"/>
+      <x:c r="G241" s="15"/>
     </x:row>
     <x:row r="242">
-      <x:c r="H242" s="18"/>
+      <x:c r="F242" s="15"/>
+      <x:c r="G242" s="15"/>
     </x:row>
     <x:row r="243">
-      <x:c r="H243" s="18"/>
+      <x:c r="F243" s="15"/>
+      <x:c r="G243" s="15"/>
     </x:row>
     <x:row r="244">
-      <x:c r="H244" s="18"/>
+      <x:c r="F244" s="15"/>
+      <x:c r="G244" s="15"/>
     </x:row>
     <x:row r="245">
-      <x:c r="H245" s="18"/>
+      <x:c r="F245" s="15"/>
+      <x:c r="G245" s="15"/>
     </x:row>
     <x:row r="246">
-      <x:c r="H246" s="18"/>
+      <x:c r="F246" s="15"/>
+      <x:c r="G246" s="15"/>
     </x:row>
     <x:row r="247">
-      <x:c r="H247" s="18"/>
+      <x:c r="F247" s="15"/>
+      <x:c r="G247" s="15"/>
     </x:row>
     <x:row r="248">
-      <x:c r="H248" s="18"/>
+      <x:c r="F248" s="15"/>
+      <x:c r="G248" s="15"/>
     </x:row>
     <x:row r="249">
-      <x:c r="H249" s="18"/>
+      <x:c r="F249" s="15"/>
+      <x:c r="G249" s="15"/>
     </x:row>
     <x:row r="250">
-      <x:c r="H250" s="18"/>
+      <x:c r="F250" s="15"/>
+      <x:c r="G250" s="15"/>
     </x:row>
     <x:row r="251">
-      <x:c r="H251" s="18"/>
+      <x:c r="F251" s="15"/>
+      <x:c r="G251" s="15"/>
     </x:row>
     <x:row r="252">
-      <x:c r="H252" s="18"/>
+      <x:c r="F252" s="15"/>
+      <x:c r="G252" s="15"/>
     </x:row>
     <x:row r="253">
-      <x:c r="H253" s="18"/>
+      <x:c r="F253" s="15"/>
+      <x:c r="G253" s="15"/>
     </x:row>
     <x:row r="254">
-      <x:c r="H254" s="18"/>
+      <x:c r="F254" s="15"/>
+      <x:c r="G254" s="15"/>
     </x:row>
     <x:row r="255">
-      <x:c r="H255" s="18"/>
+      <x:c r="F255" s="15"/>
+      <x:c r="G255" s="15"/>
     </x:row>
     <x:row r="256">
-      <x:c r="H256" s="18"/>
+      <x:c r="F256" s="15"/>
+      <x:c r="G256" s="15"/>
     </x:row>
     <x:row r="257">
-      <x:c r="H257" s="18"/>
+      <x:c r="F257" s="15"/>
+      <x:c r="G257" s="15"/>
     </x:row>
     <x:row r="258">
-      <x:c r="H258" s="18"/>
+      <x:c r="F258" s="15"/>
+      <x:c r="G258" s="15"/>
     </x:row>
     <x:row r="259">
-      <x:c r="H259" s="18"/>
+      <x:c r="F259" s="15"/>
+      <x:c r="G259" s="15"/>
     </x:row>
     <x:row r="260">
-      <x:c r="H260" s="18"/>
+      <x:c r="F260" s="15"/>
+      <x:c r="G260" s="15"/>
     </x:row>
     <x:row r="261">
-      <x:c r="H261" s="18"/>
+      <x:c r="F261" s="15"/>
+      <x:c r="G261" s="15"/>
     </x:row>
     <x:row r="262">
-      <x:c r="H262" s="18"/>
+      <x:c r="F262" s="15"/>
+      <x:c r="G262" s="15"/>
     </x:row>
     <x:row r="263">
-      <x:c r="H263" s="18"/>
+      <x:c r="F263" s="15"/>
+      <x:c r="G263" s="15"/>
     </x:row>
     <x:row r="264">
-      <x:c r="H264" s="18"/>
+      <x:c r="F264" s="15"/>
+      <x:c r="G264" s="15"/>
     </x:row>
     <x:row r="265">
-      <x:c r="H265" s="18"/>
+      <x:c r="F265" s="15"/>
+      <x:c r="G265" s="15"/>
     </x:row>
     <x:row r="266">
-      <x:c r="H266" s="18"/>
+      <x:c r="F266" s="15"/>
+      <x:c r="G266" s="15"/>
     </x:row>
     <x:row r="267">
-      <x:c r="H267" s="18"/>
+      <x:c r="F267" s="15"/>
+      <x:c r="G267" s="15"/>
     </x:row>
     <x:row r="268">
-      <x:c r="H268" s="18"/>
+      <x:c r="F268" s="15"/>
+      <x:c r="G268" s="15"/>
     </x:row>
     <x:row r="269">
-      <x:c r="H269" s="18"/>
+      <x:c r="F269" s="15"/>
+      <x:c r="G269" s="15"/>
     </x:row>
     <x:row r="270">
-      <x:c r="H270" s="18"/>
+      <x:c r="F270" s="15"/>
+      <x:c r="G270" s="15"/>
     </x:row>
     <x:row r="271">
-      <x:c r="H271" s="18"/>
+      <x:c r="F271" s="15"/>
+      <x:c r="G271" s="15"/>
     </x:row>
     <x:row r="272">
-      <x:c r="H272" s="18"/>
+      <x:c r="F272" s="15"/>
+      <x:c r="G272" s="15"/>
     </x:row>
     <x:row r="273">
-      <x:c r="H273" s="18"/>
+      <x:c r="F273" s="15"/>
+      <x:c r="G273" s="15"/>
     </x:row>
     <x:row r="274">
-      <x:c r="H274" s="18"/>
+      <x:c r="F274" s="15"/>
+      <x:c r="G274" s="15"/>
     </x:row>
     <x:row r="275">
-      <x:c r="H275" s="18"/>
+      <x:c r="F275" s="15"/>
+      <x:c r="G275" s="15"/>
     </x:row>
     <x:row r="276">
-      <x:c r="H276" s="18"/>
+      <x:c r="F276" s="15"/>
+      <x:c r="G276" s="15"/>
     </x:row>
     <x:row r="277">
-      <x:c r="H277" s="18"/>
+      <x:c r="F277" s="15"/>
+      <x:c r="G277" s="15"/>
     </x:row>
     <x:row r="278">
-      <x:c r="H278" s="18"/>
+      <x:c r="F278" s="15"/>
+      <x:c r="G278" s="15"/>
     </x:row>
     <x:row r="279">
-      <x:c r="H279" s="18"/>
+      <x:c r="F279" s="15"/>
+      <x:c r="G279" s="15"/>
     </x:row>
     <x:row r="280">
-      <x:c r="H280" s="18"/>
+      <x:c r="F280" s="15"/>
+      <x:c r="G280" s="15"/>
     </x:row>
     <x:row r="281">
-      <x:c r="H281" s="18"/>
+      <x:c r="F281" s="15"/>
+      <x:c r="G281" s="15"/>
     </x:row>
     <x:row r="282">
-      <x:c r="H282" s="18"/>
+      <x:c r="F282" s="15"/>
+      <x:c r="G282" s="15"/>
     </x:row>
     <x:row r="283">
-      <x:c r="H283" s="18"/>
+      <x:c r="F283" s="15"/>
+      <x:c r="G283" s="15"/>
     </x:row>
     <x:row r="284">
-      <x:c r="H284" s="18"/>
+      <x:c r="F284" s="15"/>
+      <x:c r="G284" s="15"/>
     </x:row>
     <x:row r="285">
-      <x:c r="H285" s="18"/>
+      <x:c r="F285" s="15"/>
+      <x:c r="G285" s="15"/>
     </x:row>
     <x:row r="286">
-      <x:c r="H286" s="18"/>
+      <x:c r="F286" s="15"/>
+      <x:c r="G286" s="15"/>
     </x:row>
     <x:row r="287">
-      <x:c r="H287" s="18"/>
+      <x:c r="F287" s="15"/>
+      <x:c r="G287" s="15"/>
     </x:row>
     <x:row r="288">
-      <x:c r="H288" s="18"/>
+      <x:c r="F288" s="15"/>
+      <x:c r="G288" s="15"/>
     </x:row>
     <x:row r="289">
-      <x:c r="H289" s="18"/>
+      <x:c r="F289" s="15"/>
+      <x:c r="G289" s="15"/>
     </x:row>
     <x:row r="290">
-      <x:c r="H290" s="18"/>
+      <x:c r="F290" s="15"/>
+      <x:c r="G290" s="15"/>
     </x:row>
     <x:row r="291">
-      <x:c r="H291" s="18"/>
+      <x:c r="F291" s="15"/>
+      <x:c r="G291" s="15"/>
     </x:row>
     <x:row r="292">
-      <x:c r="H292" s="18"/>
+      <x:c r="F292" s="15"/>
+      <x:c r="G292" s="15"/>
     </x:row>
     <x:row r="293">
-      <x:c r="H293" s="18"/>
+      <x:c r="F293" s="15"/>
+      <x:c r="G293" s="15"/>
     </x:row>
     <x:row r="294">
-      <x:c r="H294" s="18"/>
+      <x:c r="F294" s="15"/>
+      <x:c r="G294" s="15"/>
     </x:row>
     <x:row r="295">
-      <x:c r="H295" s="18"/>
+      <x:c r="F295" s="15"/>
+      <x:c r="G295" s="15"/>
     </x:row>
     <x:row r="296">
-      <x:c r="H296" s="18"/>
+      <x:c r="F296" s="15"/>
+      <x:c r="G296" s="15"/>
     </x:row>
     <x:row r="297">
-      <x:c r="H297" s="18"/>
+      <x:c r="F297" s="15"/>
+      <x:c r="G297" s="15"/>
     </x:row>
     <x:row r="298">
-      <x:c r="H298" s="18"/>
+      <x:c r="F298" s="15"/>
+      <x:c r="G298" s="15"/>
     </x:row>
     <x:row r="299">
-      <x:c r="H299" s="18"/>
+      <x:c r="F299" s="15"/>
+      <x:c r="G299" s="15"/>
     </x:row>
     <x:row r="300">
-      <x:c r="H300" s="18"/>
+      <x:c r="F300" s="15"/>
+      <x:c r="G300" s="15"/>
     </x:row>
     <x:row r="301">
-      <x:c r="H301" s="18"/>
+      <x:c r="F301" s="15"/>
+      <x:c r="G301" s="15"/>
     </x:row>
     <x:row r="302">
-      <x:c r="H302" s="18"/>
+      <x:c r="F302" s="15"/>
+      <x:c r="G302" s="15"/>
     </x:row>
     <x:row r="303">
-      <x:c r="H303" s="18"/>
+      <x:c r="F303" s="15"/>
+      <x:c r="G303" s="15"/>
     </x:row>
     <x:row r="304">
-      <x:c r="H304" s="18"/>
+      <x:c r="F304" s="15"/>
+      <x:c r="G304" s="15"/>
     </x:row>
     <x:row r="305">
-      <x:c r="H305" s="18"/>
+      <x:c r="F305" s="15"/>
+      <x:c r="G305" s="15"/>
     </x:row>
     <x:row r="306">
-      <x:c r="H306" s="18"/>
+      <x:c r="F306" s="15"/>
+      <x:c r="G306" s="15"/>
     </x:row>
     <x:row r="307">
-      <x:c r="H307" s="18"/>
+      <x:c r="F307" s="15"/>
+      <x:c r="G307" s="15"/>
     </x:row>
     <x:row r="308">
-      <x:c r="H308" s="18"/>
+      <x:c r="F308" s="15"/>
+      <x:c r="G308" s="15"/>
     </x:row>
     <x:row r="309">
-      <x:c r="H309" s="18"/>
+      <x:c r="F309" s="15"/>
+      <x:c r="G309" s="15"/>
     </x:row>
     <x:row r="310">
-      <x:c r="H310" s="18"/>
+      <x:c r="F310" s="15"/>
+      <x:c r="G310" s="15"/>
     </x:row>
     <x:row r="311">
-      <x:c r="H311" s="18"/>
+      <x:c r="F311" s="15"/>
+      <x:c r="G311" s="15"/>
     </x:row>
     <x:row r="312">
-      <x:c r="H312" s="18"/>
+      <x:c r="F312" s="15"/>
+      <x:c r="G312" s="15"/>
     </x:row>
     <x:row r="313">
-      <x:c r="H313" s="18"/>
+      <x:c r="F313" s="15"/>
+      <x:c r="G313" s="15"/>
     </x:row>
     <x:row r="314">
-      <x:c r="H314" s="18"/>
+      <x:c r="F314" s="15"/>
+      <x:c r="G314" s="15"/>
     </x:row>
     <x:row r="315">
-      <x:c r="H315" s="18"/>
+      <x:c r="F315" s="15"/>
+      <x:c r="G315" s="15"/>
     </x:row>
     <x:row r="316">
-      <x:c r="H316" s="18"/>
+      <x:c r="F316" s="15"/>
+      <x:c r="G316" s="15"/>
     </x:row>
     <x:row r="317">
-      <x:c r="H317" s="18"/>
+      <x:c r="F317" s="15"/>
+      <x:c r="G317" s="15"/>
     </x:row>
     <x:row r="318">
-      <x:c r="H318" s="18"/>
+      <x:c r="F318" s="15"/>
+      <x:c r="G318" s="15"/>
     </x:row>
     <x:row r="319">
-      <x:c r="H319" s="18"/>
+      <x:c r="F319" s="15"/>
+      <x:c r="G319" s="15"/>
     </x:row>
     <x:row r="320">
-      <x:c r="H320" s="18"/>
+      <x:c r="F320" s="15"/>
+      <x:c r="G320" s="15"/>
     </x:row>
     <x:row r="321">
-      <x:c r="H321" s="18"/>
+      <x:c r="F321" s="15"/>
+      <x:c r="G321" s="15"/>
     </x:row>
     <x:row r="322">
-      <x:c r="H322" s="18"/>
+      <x:c r="F322" s="15"/>
+      <x:c r="G322" s="15"/>
     </x:row>
     <x:row r="323">
-      <x:c r="H323" s="18"/>
+      <x:c r="F323" s="15"/>
+      <x:c r="G323" s="15"/>
     </x:row>
     <x:row r="324">
-      <x:c r="H324" s="18"/>
+      <x:c r="F324" s="15"/>
+      <x:c r="G324" s="15"/>
     </x:row>
     <x:row r="325">
-      <x:c r="H325" s="18"/>
+      <x:c r="F325" s="15"/>
+      <x:c r="G325" s="15"/>
     </x:row>
     <x:row r="326">
-      <x:c r="H326" s="18"/>
+      <x:c r="F326" s="15"/>
+      <x:c r="G326" s="15"/>
     </x:row>
     <x:row r="327">
-      <x:c r="H327" s="18"/>
+      <x:c r="F327" s="15"/>
+      <x:c r="G327" s="15"/>
     </x:row>
     <x:row r="328">
-      <x:c r="H328" s="18"/>
+      <x:c r="F328" s="15"/>
+      <x:c r="G328" s="15"/>
     </x:row>
     <x:row r="329">
-      <x:c r="H329" s="18"/>
+      <x:c r="F329" s="15"/>
+      <x:c r="G329" s="15"/>
     </x:row>
     <x:row r="330">
-      <x:c r="H330" s="18"/>
+      <x:c r="F330" s="15"/>
+      <x:c r="G330" s="15"/>
     </x:row>
     <x:row r="331">
-      <x:c r="H331" s="18"/>
+      <x:c r="F331" s="15"/>
+      <x:c r="G331" s="15"/>
     </x:row>
     <x:row r="332">
-      <x:c r="H332" s="18"/>
+      <x:c r="F332" s="15"/>
+      <x:c r="G332" s="15"/>
     </x:row>
     <x:row r="333">
-      <x:c r="H333" s="18"/>
+      <x:c r="F333" s="15"/>
+      <x:c r="G333" s="15"/>
     </x:row>
     <x:row r="334">
-      <x:c r="H334" s="18"/>
+      <x:c r="F334" s="15"/>
+      <x:c r="G334" s="15"/>
     </x:row>
     <x:row r="335">
-      <x:c r="H335" s="18"/>
+      <x:c r="F335" s="15"/>
+      <x:c r="G335" s="15"/>
     </x:row>
     <x:row r="336">
-      <x:c r="H336" s="18"/>
+      <x:c r="F336" s="15"/>
+      <x:c r="G336" s="15"/>
     </x:row>
     <x:row r="337">
-      <x:c r="H337" s="18"/>
+      <x:c r="F337" s="15"/>
+      <x:c r="G337" s="15"/>
     </x:row>
     <x:row r="338">
-      <x:c r="H338" s="18"/>
+      <x:c r="F338" s="15"/>
+      <x:c r="G338" s="15"/>
     </x:row>
     <x:row r="339">
-      <x:c r="H339" s="18"/>
+      <x:c r="F339" s="15"/>
+      <x:c r="G339" s="15"/>
     </x:row>
     <x:row r="340">
-      <x:c r="H340" s="18"/>
+      <x:c r="F340" s="15"/>
+      <x:c r="G340" s="15"/>
     </x:row>
     <x:row r="341">
-      <x:c r="H341" s="18"/>
+      <x:c r="F341" s="15"/>
+      <x:c r="G341" s="15"/>
     </x:row>
     <x:row r="342">
-      <x:c r="H342" s="18"/>
+      <x:c r="F342" s="15"/>
+      <x:c r="G342" s="15"/>
     </x:row>
     <x:row r="343">
-      <x:c r="H343" s="18"/>
+      <x:c r="F343" s="15"/>
+      <x:c r="G343" s="15"/>
     </x:row>
     <x:row r="344">
-      <x:c r="H344" s="18"/>
+      <x:c r="F344" s="15"/>
+      <x:c r="G344" s="15"/>
     </x:row>
     <x:row r="345">
-      <x:c r="H345" s="18"/>
+      <x:c r="F345" s="15"/>
+      <x:c r="G345" s="15"/>
     </x:row>
     <x:row r="346">
-      <x:c r="H346" s="18"/>
+      <x:c r="F346" s="15"/>
+      <x:c r="G346" s="15"/>
     </x:row>
     <x:row r="347">
-      <x:c r="H347" s="18"/>
+      <x:c r="F347" s="15"/>
+      <x:c r="G347" s="15"/>
     </x:row>
     <x:row r="348">
-      <x:c r="H348" s="18"/>
+      <x:c r="F348" s="15"/>
+      <x:c r="G348" s="15"/>
     </x:row>
     <x:row r="349">
-      <x:c r="H349" s="18"/>
+      <x:c r="F349" s="15"/>
+      <x:c r="G349" s="15"/>
     </x:row>
     <x:row r="350">
-      <x:c r="H350" s="18"/>
+      <x:c r="F350" s="15"/>
+      <x:c r="G350" s="15"/>
     </x:row>
     <x:row r="351">
-      <x:c r="H351" s="18"/>
+      <x:c r="F351" s="15"/>
+      <x:c r="G351" s="15"/>
     </x:row>
     <x:row r="352">
-      <x:c r="H352" s="18"/>
+      <x:c r="F352" s="15"/>
+      <x:c r="G352" s="15"/>
     </x:row>
     <x:row r="353">
-      <x:c r="H353" s="18"/>
+      <x:c r="F353" s="15"/>
+      <x:c r="G353" s="15"/>
     </x:row>
     <x:row r="354">
-      <x:c r="H354" s="18"/>
+      <x:c r="F354" s="15"/>
+      <x:c r="G354" s="15"/>
     </x:row>
     <x:row r="355">
-      <x:c r="H355" s="18"/>
+      <x:c r="F355" s="15"/>
+      <x:c r="G355" s="15"/>
     </x:row>
     <x:row r="356">
-      <x:c r="H356" s="18"/>
+      <x:c r="F356" s="15"/>
+      <x:c r="G356" s="15"/>
     </x:row>
     <x:row r="357">
-      <x:c r="H357" s="18"/>
+      <x:c r="F357" s="15"/>
+      <x:c r="G357" s="15"/>
     </x:row>
     <x:row r="358">
-      <x:c r="H358" s="18"/>
+      <x:c r="F358" s="15"/>
+      <x:c r="G358" s="15"/>
     </x:row>
     <x:row r="359">
-      <x:c r="H359" s="18"/>
+      <x:c r="F359" s="15"/>
+      <x:c r="G359" s="15"/>
     </x:row>
     <x:row r="360">
-      <x:c r="H360" s="18"/>
+      <x:c r="F360" s="15"/>
+      <x:c r="G360" s="15"/>
     </x:row>
     <x:row r="361">
-      <x:c r="H361" s="18"/>
+      <x:c r="F361" s="15"/>
+      <x:c r="G361" s="15"/>
     </x:row>
     <x:row r="362">
-      <x:c r="H362" s="18"/>
+      <x:c r="F362" s="15"/>
+      <x:c r="G362" s="15"/>
     </x:row>
     <x:row r="363">
-      <x:c r="H363" s="18"/>
+      <x:c r="F363" s="15"/>
+      <x:c r="G363" s="15"/>
     </x:row>
     <x:row r="364">
-      <x:c r="H364" s="18"/>
+      <x:c r="F364" s="15"/>
+      <x:c r="G364" s="15"/>
     </x:row>
     <x:row r="365">
-      <x:c r="H365" s="18"/>
+      <x:c r="F365" s="15"/>
+      <x:c r="G365" s="15"/>
     </x:row>
     <x:row r="366">
-      <x:c r="H366" s="18"/>
+      <x:c r="F366" s="15"/>
+      <x:c r="G366" s="15"/>
     </x:row>
     <x:row r="367">
-      <x:c r="H367" s="18"/>
+      <x:c r="F367" s="15"/>
+      <x:c r="G367" s="15"/>
     </x:row>
     <x:row r="368">
-      <x:c r="H368" s="18"/>
+      <x:c r="F368" s="15"/>
+      <x:c r="G368" s="15"/>
     </x:row>
     <x:row r="369">
-      <x:c r="H369" s="18"/>
+      <x:c r="F369" s="15"/>
+      <x:c r="G369" s="15"/>
     </x:row>
     <x:row r="370">
-      <x:c r="H370" s="18"/>
+      <x:c r="F370" s="15"/>
+      <x:c r="G370" s="15"/>
     </x:row>
     <x:row r="371">
-      <x:c r="H371" s="18"/>
+      <x:c r="F371" s="15"/>
+      <x:c r="G371" s="15"/>
     </x:row>
     <x:row r="372">
-      <x:c r="H372" s="18"/>
+      <x:c r="F372" s="15"/>
+      <x:c r="G372" s="15"/>
     </x:row>
     <x:row r="373">
-      <x:c r="H373" s="18"/>
+      <x:c r="F373" s="15"/>
+      <x:c r="G373" s="15"/>
     </x:row>
     <x:row r="374">
-      <x:c r="H374" s="18"/>
+      <x:c r="F374" s="15"/>
+      <x:c r="G374" s="15"/>
     </x:row>
     <x:row r="375">
-      <x:c r="H375" s="18"/>
+      <x:c r="F375" s="15"/>
+      <x:c r="G375" s="15"/>
     </x:row>
     <x:row r="376">
-      <x:c r="H376" s="18"/>
+      <x:c r="F376" s="15"/>
+      <x:c r="G376" s="15"/>
     </x:row>
     <x:row r="377">
-      <x:c r="H377" s="18"/>
+      <x:c r="F377" s="15"/>
+      <x:c r="G377" s="15"/>
     </x:row>
     <x:row r="378">
-      <x:c r="H378" s="18"/>
+      <x:c r="F378" s="15"/>
+      <x:c r="G378" s="15"/>
     </x:row>
     <x:row r="379">
-      <x:c r="H379" s="18"/>
+      <x:c r="F379" s="15"/>
+      <x:c r="G379" s="15"/>
     </x:row>
     <x:row r="380">
-      <x:c r="H380" s="18"/>
+      <x:c r="F380" s="15"/>
+      <x:c r="G380" s="15"/>
     </x:row>
     <x:row r="381">
-      <x:c r="H381" s="18"/>
+      <x:c r="F381" s="15"/>
+      <x:c r="G381" s="15"/>
     </x:row>
     <x:row r="382">
-      <x:c r="H382" s="18"/>
+      <x:c r="F382" s="15"/>
+      <x:c r="G382" s="15"/>
     </x:row>
     <x:row r="383">
-      <x:c r="H383" s="18"/>
+      <x:c r="F383" s="15"/>
+      <x:c r="G383" s="15"/>
     </x:row>
     <x:row r="384">
-      <x:c r="H384" s="18"/>
+      <x:c r="F384" s="15"/>
+      <x:c r="G384" s="15"/>
     </x:row>
     <x:row r="385">
-      <x:c r="H385" s="18"/>
+      <x:c r="F385" s="15"/>
+      <x:c r="G385" s="15"/>
     </x:row>
     <x:row r="386">
-      <x:c r="H386" s="18"/>
+      <x:c r="F386" s="15"/>
+      <x:c r="G386" s="15"/>
     </x:row>
     <x:row r="387">
-      <x:c r="H387" s="18"/>
+      <x:c r="F387" s="15"/>
+      <x:c r="G387" s="15"/>
     </x:row>
     <x:row r="388">
-      <x:c r="H388" s="18"/>
+      <x:c r="F388" s="15"/>
+      <x:c r="G388" s="15"/>
     </x:row>
     <x:row r="389">
-      <x:c r="H389" s="18"/>
+      <x:c r="F389" s="15"/>
+      <x:c r="G389" s="15"/>
     </x:row>
     <x:row r="390">
-      <x:c r="H390" s="18"/>
+      <x:c r="F390" s="15"/>
+      <x:c r="G390" s="15"/>
     </x:row>
     <x:row r="391">
-      <x:c r="H391" s="18"/>
+      <x:c r="F391" s="15"/>
+      <x:c r="G391" s="15"/>
     </x:row>
     <x:row r="392">
-      <x:c r="H392" s="18"/>
+      <x:c r="F392" s="15"/>
+      <x:c r="G392" s="15"/>
     </x:row>
     <x:row r="393">
-      <x:c r="H393" s="18"/>
+      <x:c r="F393" s="15"/>
+      <x:c r="G393" s="15"/>
     </x:row>
     <x:row r="394">
-      <x:c r="H394" s="18"/>
+      <x:c r="F394" s="15"/>
+      <x:c r="G394" s="15"/>
     </x:row>
     <x:row r="395">
-      <x:c r="H395" s="18"/>
+      <x:c r="F395" s="15"/>
+      <x:c r="G395" s="15"/>
     </x:row>
     <x:row r="396">
-      <x:c r="H396" s="18"/>
+      <x:c r="F396" s="15"/>
+      <x:c r="G396" s="15"/>
     </x:row>
     <x:row r="397">
-      <x:c r="H397" s="18"/>
+      <x:c r="F397" s="15"/>
+      <x:c r="G397" s="15"/>
     </x:row>
     <x:row r="398">
-      <x:c r="H398" s="18"/>
+      <x:c r="F398" s="15"/>
+      <x:c r="G398" s="15"/>
     </x:row>
     <x:row r="399">
-      <x:c r="H399" s="18"/>
+      <x:c r="F399" s="15"/>
+      <x:c r="G399" s="15"/>
     </x:row>
     <x:row r="400">
-      <x:c r="H400" s="18"/>
+      <x:c r="F400" s="15"/>
+      <x:c r="G400" s="15"/>
     </x:row>
     <x:row r="401">
-      <x:c r="H401" s="18"/>
+      <x:c r="F401" s="15"/>
+      <x:c r="G401" s="15"/>
     </x:row>
     <x:row r="402">
-      <x:c r="H402" s="18"/>
+      <x:c r="F402" s="15"/>
+      <x:c r="G402" s="15"/>
     </x:row>
     <x:row r="403">
-      <x:c r="H403" s="18"/>
+      <x:c r="F403" s="15"/>
+      <x:c r="G403" s="15"/>
     </x:row>
     <x:row r="404">
-      <x:c r="H404" s="18"/>
+      <x:c r="F404" s="15"/>
+      <x:c r="G404" s="15"/>
     </x:row>
     <x:row r="405">
-      <x:c r="H405" s="18"/>
+      <x:c r="F405" s="15"/>
+      <x:c r="G405" s="15"/>
     </x:row>
     <x:row r="406">
-      <x:c r="H406" s="18"/>
+      <x:c r="F406" s="15"/>
+      <x:c r="G406" s="15"/>
     </x:row>
     <x:row r="407">
-      <x:c r="H407" s="18"/>
+      <x:c r="F407" s="15"/>
+      <x:c r="G407" s="15"/>
     </x:row>
     <x:row r="408">
-      <x:c r="H408" s="18"/>
+      <x:c r="F408" s="15"/>
+      <x:c r="G408" s="15"/>
     </x:row>
     <x:row r="409">
-      <x:c r="H409" s="18"/>
+      <x:c r="F409" s="15"/>
+      <x:c r="G409" s="15"/>
     </x:row>
     <x:row r="410">
-      <x:c r="H410" s="18"/>
+      <x:c r="F410" s="15"/>
+      <x:c r="G410" s="15"/>
     </x:row>
     <x:row r="411">
-      <x:c r="H411" s="18"/>
+      <x:c r="F411" s="15"/>
+      <x:c r="G411" s="15"/>
     </x:row>
     <x:row r="412">
-      <x:c r="H412" s="18"/>
+      <x:c r="F412" s="15"/>
+      <x:c r="G412" s="15"/>
     </x:row>
     <x:row r="413">
-      <x:c r="H413" s="18"/>
+      <x:c r="F413" s="15"/>
+      <x:c r="G413" s="15"/>
     </x:row>
     <x:row r="414">
-      <x:c r="H414" s="18"/>
+      <x:c r="F414" s="15"/>
+      <x:c r="G414" s="15"/>
     </x:row>
     <x:row r="415">
-      <x:c r="H415" s="18"/>
+      <x:c r="F415" s="15"/>
+      <x:c r="G415" s="15"/>
     </x:row>
     <x:row r="416">
-      <x:c r="H416" s="18"/>
+      <x:c r="F416" s="15"/>
+      <x:c r="G416" s="15"/>
     </x:row>
     <x:row r="417">
-      <x:c r="H417" s="18"/>
+      <x:c r="F417" s="15"/>
+      <x:c r="G417" s="15"/>
     </x:row>
     <x:row r="418">
-      <x:c r="H418" s="18"/>
+      <x:c r="F418" s="15"/>
+      <x:c r="G418" s="15"/>
     </x:row>
     <x:row r="419">
-      <x:c r="H419" s="18"/>
+      <x:c r="F419" s="15"/>
+      <x:c r="G419" s="15"/>
     </x:row>
     <x:row r="420">
-      <x:c r="H420" s="18"/>
+      <x:c r="F420" s="15"/>
+      <x:c r="G420" s="15"/>
     </x:row>
     <x:row r="421">
-      <x:c r="H421" s="18"/>
+      <x:c r="F421" s="15"/>
+      <x:c r="G421" s="15"/>
     </x:row>
     <x:row r="422">
-      <x:c r="H422" s="18"/>
+      <x:c r="F422" s="15"/>
+      <x:c r="G422" s="15"/>
     </x:row>
     <x:row r="423">
-      <x:c r="H423" s="18"/>
+      <x:c r="F423" s="15"/>
+      <x:c r="G423" s="15"/>
     </x:row>
     <x:row r="424">
-      <x:c r="H424" s="18"/>
+      <x:c r="F424" s="15"/>
+      <x:c r="G424" s="15"/>
     </x:row>
     <x:row r="425">
-      <x:c r="H425" s="18"/>
+      <x:c r="F425" s="15"/>
+      <x:c r="G425" s="15"/>
     </x:row>
     <x:row r="426">
-      <x:c r="H426" s="18"/>
+      <x:c r="F426" s="15"/>
+      <x:c r="G426" s="15"/>
     </x:row>
     <x:row r="427">
-      <x:c r="H427" s="18"/>
+      <x:c r="F427" s="15"/>
+      <x:c r="G427" s="15"/>
     </x:row>
     <x:row r="428">
-      <x:c r="H428" s="18"/>
+      <x:c r="F428" s="15"/>
+      <x:c r="G428" s="15"/>
     </x:row>
     <x:row r="429">
-      <x:c r="H429" s="18"/>
+      <x:c r="F429" s="15"/>
+      <x:c r="G429" s="15"/>
     </x:row>
     <x:row r="430">
-      <x:c r="H430" s="18"/>
+      <x:c r="F430" s="15"/>
+      <x:c r="G430" s="15"/>
     </x:row>
     <x:row r="431">
-      <x:c r="H431" s="18"/>
+      <x:c r="F431" s="15"/>
+      <x:c r="G431" s="15"/>
     </x:row>
     <x:row r="432">
-      <x:c r="H432" s="18"/>
+      <x:c r="F432" s="15"/>
+      <x:c r="G432" s="15"/>
     </x:row>
     <x:row r="433">
-      <x:c r="H433" s="18"/>
+      <x:c r="F433" s="15"/>
+      <x:c r="G433" s="15"/>
     </x:row>
     <x:row r="434">
-      <x:c r="H434" s="18"/>
+      <x:c r="F434" s="15"/>
+      <x:c r="G434" s="15"/>
     </x:row>
     <x:row r="435">
-      <x:c r="H435" s="18"/>
+      <x:c r="F435" s="15"/>
+      <x:c r="G435" s="15"/>
     </x:row>
     <x:row r="436">
-      <x:c r="H436" s="18"/>
+      <x:c r="F436" s="15"/>
+      <x:c r="G436" s="15"/>
     </x:row>
     <x:row r="437">
-      <x:c r="H437" s="18"/>
+      <x:c r="F437" s="15"/>
+      <x:c r="G437" s="15"/>
     </x:row>
     <x:row r="438">
-      <x:c r="H438" s="18"/>
+      <x:c r="F438" s="15"/>
+      <x:c r="G438" s="15"/>
     </x:row>
     <x:row r="439">
-      <x:c r="H439" s="18"/>
+      <x:c r="F439" s="15"/>
+      <x:c r="G439" s="15"/>
     </x:row>
     <x:row r="440">
-      <x:c r="H440" s="18"/>
+      <x:c r="F440" s="15"/>
+      <x:c r="G440" s="15"/>
     </x:row>
     <x:row r="441">
-      <x:c r="H441" s="18"/>
+      <x:c r="F441" s="15"/>
+      <x:c r="G441" s="15"/>
     </x:row>
     <x:row r="442">
-      <x:c r="H442" s="18"/>
+      <x:c r="F442" s="15"/>
+      <x:c r="G442" s="15"/>
     </x:row>
     <x:row r="443">
-      <x:c r="H443" s="18"/>
+      <x:c r="F443" s="15"/>
+      <x:c r="G443" s="15"/>
     </x:row>
     <x:row r="444">
-      <x:c r="H444" s="18"/>
+      <x:c r="F444" s="15"/>
+      <x:c r="G444" s="15"/>
     </x:row>
     <x:row r="445">
-      <x:c r="H445" s="18"/>
+      <x:c r="F445" s="15"/>
+      <x:c r="G445" s="15"/>
     </x:row>
     <x:row r="446">
-      <x:c r="H446" s="18"/>
+      <x:c r="F446" s="15"/>
+      <x:c r="G446" s="15"/>
     </x:row>
     <x:row r="447">
-      <x:c r="H447" s="18"/>
+      <x:c r="F447" s="15"/>
+      <x:c r="G447" s="15"/>
     </x:row>
     <x:row r="448">
-      <x:c r="H448" s="18"/>
+      <x:c r="F448" s="15"/>
+      <x:c r="G448" s="15"/>
     </x:row>
     <x:row r="449">
-      <x:c r="H449" s="18"/>
+      <x:c r="F449" s="15"/>
+      <x:c r="G449" s="15"/>
     </x:row>
     <x:row r="450">
-      <x:c r="H450" s="18"/>
+      <x:c r="F450" s="15"/>
+      <x:c r="G450" s="15"/>
     </x:row>
     <x:row r="451">
-      <x:c r="H451" s="18"/>
+      <x:c r="F451" s="15"/>
+      <x:c r="G451" s="15"/>
     </x:row>
     <x:row r="452">
-      <x:c r="H452" s="18"/>
+      <x:c r="F452" s="15"/>
+      <x:c r="G452" s="15"/>
     </x:row>
     <x:row r="453">
-      <x:c r="H453" s="18"/>
+      <x:c r="F453" s="15"/>
+      <x:c r="G453" s="15"/>
     </x:row>
     <x:row r="454">
-      <x:c r="H454" s="18"/>
+      <x:c r="F454" s="15"/>
+      <x:c r="G454" s="15"/>
     </x:row>
     <x:row r="455">
-      <x:c r="H455" s="18"/>
+      <x:c r="F455" s="15"/>
+      <x:c r="G455" s="15"/>
     </x:row>
     <x:row r="456">
-      <x:c r="H456" s="18"/>
+      <x:c r="F456" s="15"/>
+      <x:c r="G456" s="15"/>
     </x:row>
     <x:row r="457">
-      <x:c r="H457" s="18"/>
+      <x:c r="F457" s="15"/>
+      <x:c r="G457" s="15"/>
     </x:row>
     <x:row r="458">
-      <x:c r="H458" s="18"/>
+      <x:c r="F458" s="15"/>
+      <x:c r="G458" s="15"/>
     </x:row>
     <x:row r="459">
-      <x:c r="H459" s="18"/>
+      <x:c r="F459" s="15"/>
+      <x:c r="G459" s="15"/>
     </x:row>
     <x:row r="460">
-      <x:c r="H460" s="18"/>
+      <x:c r="F460" s="15"/>
+      <x:c r="G460" s="15"/>
     </x:row>
     <x:row r="461">
-      <x:c r="H461" s="18"/>
+      <x:c r="F461" s="15"/>
+      <x:c r="G461" s="15"/>
     </x:row>
     <x:row r="462">
-      <x:c r="H462" s="18"/>
+      <x:c r="F462" s="15"/>
+      <x:c r="G462" s="15"/>
     </x:row>
     <x:row r="463">
-      <x:c r="H463" s="18"/>
+      <x:c r="F463" s="15"/>
+      <x:c r="G463" s="15"/>
     </x:row>
     <x:row r="464">
-      <x:c r="H464" s="18"/>
+      <x:c r="F464" s="15"/>
+      <x:c r="G464" s="15"/>
     </x:row>
     <x:row r="465">
-      <x:c r="H465" s="18"/>
+      <x:c r="F465" s="15"/>
+      <x:c r="G465" s="15"/>
     </x:row>
     <x:row r="466">
-      <x:c r="H466" s="18"/>
+      <x:c r="F466" s="15"/>
+      <x:c r="G466" s="15"/>
     </x:row>
     <x:row r="467">
-      <x:c r="H467" s="18"/>
+      <x:c r="F467" s="15"/>
+      <x:c r="G467" s="15"/>
     </x:row>
     <x:row r="468">
-      <x:c r="H468" s="18"/>
+      <x:c r="F468" s="15"/>
+      <x:c r="G468" s="15"/>
     </x:row>
     <x:row r="469">
-      <x:c r="H469" s="18"/>
+      <x:c r="F469" s="15"/>
+      <x:c r="G469" s="15"/>
     </x:row>
     <x:row r="470">
-      <x:c r="H470" s="18"/>
+      <x:c r="F470" s="15"/>
+      <x:c r="G470" s="15"/>
     </x:row>
     <x:row r="471">
-      <x:c r="H471" s="18"/>
+      <x:c r="F471" s="15"/>
+      <x:c r="G471" s="15"/>
     </x:row>
     <x:row r="472">
-      <x:c r="H472" s="18"/>
+      <x:c r="F472" s="15"/>
+      <x:c r="G472" s="15"/>
     </x:row>
     <x:row r="473">
-      <x:c r="H473" s="18"/>
+      <x:c r="F473" s="15"/>
+      <x:c r="G473" s="15"/>
     </x:row>
     <x:row r="474">
-      <x:c r="H474" s="18"/>
+      <x:c r="F474" s="15"/>
+      <x:c r="G474" s="15"/>
     </x:row>
     <x:row r="475">
-      <x:c r="H475" s="18"/>
+      <x:c r="F475" s="15"/>
+      <x:c r="G475" s="15"/>
     </x:row>
     <x:row r="476">
-      <x:c r="H476" s="18"/>
+      <x:c r="F476" s="15"/>
+      <x:c r="G476" s="15"/>
     </x:row>
     <x:row r="477">
-      <x:c r="H477" s="18"/>
+      <x:c r="F477" s="15"/>
+      <x:c r="G477" s="15"/>
     </x:row>
     <x:row r="478">
-      <x:c r="H478" s="18"/>
+      <x:c r="F478" s="15"/>
+      <x:c r="G478" s="15"/>
     </x:row>
     <x:row r="479">
-      <x:c r="H479" s="18"/>
+      <x:c r="F479" s="15"/>
+      <x:c r="G479" s="15"/>
     </x:row>
     <x:row r="480">
-      <x:c r="H480" s="18"/>
+      <x:c r="F480" s="15"/>
+      <x:c r="G480" s="15"/>
     </x:row>
     <x:row r="481">
-      <x:c r="H481" s="18"/>
+      <x:c r="F481" s="15"/>
+      <x:c r="G481" s="15"/>
     </x:row>
     <x:row r="482">
-      <x:c r="H482" s="18"/>
+      <x:c r="F482" s="15"/>
+      <x:c r="G482" s="15"/>
     </x:row>
     <x:row r="483">
-      <x:c r="H483" s="18"/>
+      <x:c r="F483" s="15"/>
+      <x:c r="G483" s="15"/>
     </x:row>
     <x:row r="484">
-      <x:c r="H484" s="18"/>
+      <x:c r="F484" s="15"/>
+      <x:c r="G484" s="15"/>
     </x:row>
     <x:row r="485">
-      <x:c r="H485" s="18"/>
+      <x:c r="F485" s="15"/>
+      <x:c r="G485" s="15"/>
     </x:row>
     <x:row r="486">
-      <x:c r="H486" s="18"/>
+      <x:c r="F486" s="15"/>
+      <x:c r="G486" s="15"/>
     </x:row>
     <x:row r="487">
-      <x:c r="H487" s="18"/>
+      <x:c r="F487" s="15"/>
+      <x:c r="G487" s="15"/>
     </x:row>
     <x:row r="488">
-      <x:c r="H488" s="18"/>
+      <x:c r="F488" s="15"/>
+      <x:c r="G488" s="15"/>
     </x:row>
     <x:row r="489">
-      <x:c r="H489" s="18"/>
+      <x:c r="F489" s="15"/>
+      <x:c r="G489" s="15"/>
     </x:row>
     <x:row r="490">
-      <x:c r="H490" s="18"/>
+      <x:c r="F490" s="15"/>
+      <x:c r="G490" s="15"/>
     </x:row>
     <x:row r="491">
-      <x:c r="H491" s="18"/>
+      <x:c r="F491" s="15"/>
+      <x:c r="G491" s="15"/>
     </x:row>
     <x:row r="492">
-      <x:c r="H492" s="18"/>
+      <x:c r="F492" s="15"/>
+      <x:c r="G492" s="15"/>
     </x:row>
     <x:row r="493">
-      <x:c r="H493" s="18"/>
+      <x:c r="F493" s="15"/>
+      <x:c r="G493" s="15"/>
     </x:row>
     <x:row r="494">
-      <x:c r="H494" s="18"/>
+      <x:c r="F494" s="15"/>
+      <x:c r="G494" s="15"/>
     </x:row>
     <x:row r="495">
-      <x:c r="H495" s="18"/>
+      <x:c r="F495" s="15"/>
+      <x:c r="G495" s="15"/>
     </x:row>
     <x:row r="496">
-      <x:c r="H496" s="18"/>
+      <x:c r="F496" s="15"/>
+      <x:c r="G496" s="15"/>
     </x:row>
     <x:row r="497">
-      <x:c r="H497" s="18"/>
+      <x:c r="F497" s="15"/>
+      <x:c r="G497" s="15"/>
     </x:row>
     <x:row r="498">
-      <x:c r="H498" s="18"/>
+      <x:c r="F498" s="15"/>
+      <x:c r="G498" s="15"/>
     </x:row>
     <x:row r="499">
-      <x:c r="H499" s="18"/>
+      <x:c r="F499" s="15"/>
+      <x:c r="G499" s="15"/>
     </x:row>
     <x:row r="500">
-      <x:c r="H500" s="18"/>
+      <x:c r="F500" s="15"/>
+      <x:c r="G500" s="15"/>
+    </x:row>
+    <x:row r="501">
+      <x:c r="F501" s="15"/>
+      <x:c r="G501" s="15"/>
     </x:row>
   </x:sheetData>
-  <x:dataValidations count="4">
-    <x:dataValidation type="list" sqref="D2:D500">
-      <x:formula1>'Opciones válidas'!$A$2:$A$5</x:formula1>
-    </x:dataValidation>
-    <x:dataValidation type="list" sqref="G2:G500">
-      <x:formula1>'Opciones válidas'!$B$2:$B$5</x:formula1>
-    </x:dataValidation>
-    <x:dataValidation type="list" sqref="J2:J500">
-      <x:formula1>'Opciones válidas'!$C$2:$C$4</x:formula1>
-    </x:dataValidation>
-    <x:dataValidation type="decimal" operator="greaterThanOrEqual" sqref="H2:H500">
-      <x:formula1>0</x:formula1>
+  <x:conditionalFormatting sqref="H2:H501">
+    <x:cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="STOCK"/>
+    <x:cfRule type="containsText" dxfId="1" priority="2" operator="containsText" text="SOLD"/>
+  </x:conditionalFormatting>
+  <x:dataValidations count="1">
+    <x:dataValidation type="list" sqref="H2:H501">
+      <x:formula1>"STOCK,SOLD"</x:formula1>
     </x:dataValidation>
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <x:tableParts count="1">
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3a05f1a30fac4021"/>
+  </x:tableParts>
 </x:worksheet>
 </file>
 
@@ -1948,65 +2483,56 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="27" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="27" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="27" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="7" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="72" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1">
-      <x:c r="A1" s="2" t="str">
-        <x:v>Categorías</x:v>
+    <x:row r="1" ht="30" customHeight="1">
+      <x:c r="A1" s="17" t="str">
+        <x:v>CÓMO USAR LA PLANTILLA STORE MAY</x:v>
       </x:c>
-      <x:c r="B1" s="2" t="str">
-        <x:v>Géneros</x:v>
+      <x:c r="B1" s="17"/>
+      <x:c r="C1" s="17"/>
+      <x:c r="D1" s="17"/>
+      <x:c r="E1" s="17"/>
+      <x:c r="F1" s="17"/>
+    </x:row>
+    <x:row r="3" ht="32" customHeight="1">
+      <x:c r="A3" s="19" t="str">
+        <x:v>1</x:v>
       </x:c>
-      <x:c r="C1" s="2" t="str">
-        <x:v>Estados</x:v>
+      <x:c r="B3" s="21" t="str">
+        <x:v>Conserva los ocho encabezados de la hoja Productos exactamente como están.</x:v>
       </x:c>
     </x:row>
-    <x:row r="2">
-      <x:c r="A2" s="14" t="str">
-        <x:v>Mujer</x:v>
+    <x:row r="4" ht="32" customHeight="1">
+      <x:c r="A4" s="19" t="str">
+        <x:v>2</x:v>
       </x:c>
-      <x:c r="B2" s="14" t="str">
-        <x:v>Mujer</x:v>
+      <x:c r="B4" s="21" t="str">
+        <x:v>Agrega una fila por producto. Los precios deben ser números, sin fórmulas.</x:v>
       </x:c>
-      <x:c r="C2" s="14" t="str">
-        <x:v>Disponible</x:v>
+    </x:row>
+    <x:row r="5" ht="32" customHeight="1">
+      <x:c r="A5" s="19" t="str">
+        <x:v>3</x:v>
       </x:c>
-    </x:row>
-    <x:row r="3">
-      <x:c r="A3" s="19" t="str">
-        <x:v>Hombre</x:v>
+      <x:c r="B5" s="21" t="str">
+        <x:v>Nombra cada foto usando palabras del ARTICULO y MODELO para mejorar el match automático.</x:v>
       </x:c>
-      <x:c r="B3" s="19" t="str">
-        <x:v>Hombre</x:v>
+    </x:row>
+    <x:row r="6" ht="32" customHeight="1">
+      <x:c r="A6" s="19" t="str">
+        <x:v>4</x:v>
       </x:c>
-      <x:c r="C3" s="19" t="str">
-        <x:v>Agotado</x:v>
+      <x:c r="B6" s="21" t="str">
+        <x:v>En ESTADO selecciona STOCK si está disponible o SOLD si está vendido.</x:v>
       </x:c>
     </x:row>
-    <x:row r="4">
-      <x:c r="A4" s="19" t="str">
-        <x:v>Niños</x:v>
-      </x:c>
-      <x:c r="B4" s="19" t="str">
-        <x:v>Niños</x:v>
-      </x:c>
-      <x:c r="C4" s="19" t="str">
-        <x:v>Confirmar disponibilidad</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5">
-      <x:c r="A5" s="20" t="str">
-        <x:v>Accesorios</x:v>
-      </x:c>
-      <x:c r="B5" s="20" t="str">
-        <x:v>Unisex</x:v>
-      </x:c>
-      <x:c r="C5" s="20"/>
-    </x:row>
   </x:sheetData>
+  <x:mergeCells>
+    <x:mergeCell ref="A1:F1"/>
+  </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
 </file>